--- a/outputs/build/diagnostics/ref_nonmonotonic.xlsx
+++ b/outputs/build/diagnostics/ref_nonmonotonic.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="31" uniqueCount="29">
   <si>
     <t>pull_item</t>
   </si>
@@ -79,6 +79,12 @@
   </si>
   <si>
     <t>d_reclassified</t>
+  </si>
+  <si>
+    <t>source_nsu_units_here</t>
+  </si>
+  <si>
+    <t>source_nsu_units_item</t>
   </si>
   <si>
     <t>fallback_level</t>
@@ -139,7 +145,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -189,13 +195,19 @@
         <v>22</v>
       </c>
       <c r="P1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q1" t="s">
         <v>24</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>25</v>
       </c>
       <c r="R1" t="s">
         <v>26</v>
+      </c>
+      <c r="S1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="2">
@@ -242,15 +254,21 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>23</v>
-      </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="P2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>25</v>
       </c>
       <c r="R2" s="1">
+        <v>0</v>
+      </c>
+      <c r="S2" s="1">
+        <v>0</v>
+      </c>
+      <c r="T2" s="1">
         <v>1</v>
       </c>
     </row>
